--- a/詳細設計/01E_DB詳細設計書テンプレート.xlsx
+++ b/詳細設計/01E_DB詳細設計書テンプレート.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:workbook xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <ns0:sheets>
-    <ns0:sheet name="00_表紙" sheetId="1" ns1:id="Rf08b4f3278d149ae"/>
-    <ns0:sheet name="01_改訂履歴" sheetId="2" ns1:id="R6052cd0f3f68456b"/>
-    <ns0:sheet name="02_Table一覧・作成順" sheetId="3" ns1:id="Rfe2084ce2e2c4436"/>
-    <ns0:sheet name="03_ER・制約一覧" sheetId="4" ns1:id="Rcf305144b1bf46d6"/>
-    <ns0:sheet name="04_Table詳細・DDL" sheetId="5" ns1:id="R4f3b5d5c3d364a07"/>
-    <ns0:sheet name="99_Status・初期Data" sheetId="6" ns1:id="Raedcc3e7b20e4f0c"/>
-    <ns0:sheet name="05_単体テスト観点" sheetId="7" ns1:id="R2234cc1b138c4184"/>
-  </ns0:sheets>
-</ns0:workbook>
+<x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheets>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Rbc03d6df082a4610"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rda4ec3fbb0594154"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Table一覧・作成順" sheetId="3" r:id="Rf82fb5fcd9d84638"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_ER・制約一覧" sheetId="4" r:id="Rbb61c22de1734105"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Table詳細・DDL" sheetId="5" r:id="R79700ca164984571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_Status・初期Data" sheetId="6" r:id="R2840fb41715e4e6f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_単体テスト観点" sheetId="7" r:id="R9d474efad39a4ff7"/>
+  </x:sheets>
+</x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
@@ -19,6 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:numFmts count="1">
+    <x:numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
+  </x:numFmts>
   <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
@@ -120,7 +123,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="24">
+  <x:cellXfs count="26">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -174,6 +177,10 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -430,7 +437,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -574,7 +581,7 @@
       <x:c r="E12" s="14"/>
       <x:c r="F12" s="14"/>
       <x:c r="G12" s="14" t="str">
-        <x:v>Review中</x:v>
+        <x:v>Review済／承認待ち</x:v>
       </x:c>
       <x:c r="H12" s="14"/>
       <x:c r="I12" s="14"/>
@@ -630,7 +637,7 @@
       <x:c r="K15" s="15"/>
       <x:c r="L15" s="15"/>
     </x:row>
-    <x:row r="16" ht="34" customHeight="1">
+    <x:row r="16" ht="60" customHeight="1">
       <x:c r="A16" s="14" t="str">
         <x:v>参照Baseline</x:v>
       </x:c>
@@ -640,7 +647,8 @@
       <x:c r="E16" s="14"/>
       <x:c r="F16" s="14"/>
       <x:c r="G16" s="14" t="str">
-        <x:v>BL-2026-09-24＋各参照文書の最新改訂</x:v>
+        <x:v>&lt;&lt;適用Baseline ID&gt;&gt;／&lt;&lt;適用Change ID&gt;&gt;
+参照Versionは02の参照資料欄へ適用時に固定記載する。</x:v>
       </x:c>
       <x:c r="H16" s="14"/>
       <x:c r="I16" s="14"/>
@@ -684,9 +692,9 @@
       <x:c r="K18" s="14"/>
       <x:c r="L18" s="14"/>
     </x:row>
-    <x:row r="19" ht="29" customHeight="1">
+    <x:row r="19" ht="36" customHeight="1">
       <x:c r="A19" s="17" t="str">
-        <x:v>責任者欄は署名時に記入。文書状態は承認操作までReview中。</x:v>
+        <x:v>二次Review：2026-09-30。責任者欄は署名時に記入。正式承認まで承認待ちとする。</x:v>
       </x:c>
       <x:c r="B19" s="17"/>
       <x:c r="C19" s="17"/>
@@ -705,7 +713,6 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A7:F7"/>
     <x:mergeCell ref="G7:L7"/>
@@ -718,7 +725,6 @@
     <x:mergeCell ref="A11:F11"/>
     <x:mergeCell ref="G11:L11"/>
     <x:mergeCell ref="A12:F12"/>
-    <x:mergeCell ref="G12:L12"/>
     <x:mergeCell ref="A13:F13"/>
     <x:mergeCell ref="G13:L13"/>
     <x:mergeCell ref="A14:F14"/>
@@ -726,12 +732,14 @@
     <x:mergeCell ref="A15:F15"/>
     <x:mergeCell ref="G15:L15"/>
     <x:mergeCell ref="A16:F16"/>
-    <x:mergeCell ref="G16:L16"/>
     <x:mergeCell ref="A17:F17"/>
     <x:mergeCell ref="G17:L17"/>
     <x:mergeCell ref="A18:F18"/>
     <x:mergeCell ref="G18:L18"/>
+    <x:mergeCell ref="G12:L12"/>
     <x:mergeCell ref="A19:L19"/>
+    <x:mergeCell ref="A3:L3"/>
+    <x:mergeCell ref="G16:L16"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -794,7 +802,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -940,12 +948,41 @@
       </x:c>
       <x:c r="L10" s="23"/>
     </x:row>
+    <x:row r="11" ht="110" customHeight="1">
+      <x:c r="A11" s="20" t="str">
+        <x:v>Ver.2.2</x:v>
+      </x:c>
+      <x:c r="B11" s="25" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="C11" s="20"/>
+      <x:c r="D11" s="20" t="str">
+        <x:v>Review</x:v>
+      </x:c>
+      <x:c r="E11" s="20" t="str">
+        <x:v>二次Review完了。参照Baseline／Versionを適用時記入欄へ変更。設計構成は維持。</x:v>
+      </x:c>
+      <x:c r="F11" s="20"/>
+      <x:c r="G11" s="20" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="H11" s="20" t="str">
+        <x:v>Review済</x:v>
+      </x:c>
+      <x:c r="I11" s="20"/>
+      <x:c r="J11" s="20" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="K11" s="20" t="str">
+        <x:v>承認待ち</x:v>
+      </x:c>
+      <x:c r="L11" s="20"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="B7:C7"/>
     <x:mergeCell ref="E7:F7"/>
@@ -963,6 +1000,11 @@
     <x:mergeCell ref="E10:F10"/>
     <x:mergeCell ref="H10:I10"/>
     <x:mergeCell ref="K10:L10"/>
+    <x:mergeCell ref="A3:L3"/>
+    <x:mergeCell ref="B11:C11"/>
+    <x:mergeCell ref="E11:F11"/>
+    <x:mergeCell ref="H11:I11"/>
+    <x:mergeCell ref="K11:L11"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1025,7 +1067,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -1487,7 +1529,7 @@
       <x:c r="K28" s="11"/>
       <x:c r="L28" s="11"/>
     </x:row>
-    <x:row r="29" ht="34" customHeight="1">
+    <x:row r="29" ht="45" customHeight="1">
       <x:c r="A29" s="14" t="str">
         <x:v>15_DB基本設計書</x:v>
       </x:c>
@@ -1495,7 +1537,7 @@
       <x:c r="C29" s="14"/>
       <x:c r="D29" s="14"/>
       <x:c r="E29" s="14" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>&lt;&lt;適用時の正本Version&gt;&gt;</x:v>
       </x:c>
       <x:c r="F29" s="14"/>
       <x:c r="G29" s="14"/>
@@ -1507,7 +1549,7 @@
       <x:c r="K29" s="14"/>
       <x:c r="L29" s="14"/>
     </x:row>
-    <x:row r="30" ht="34" customHeight="1">
+    <x:row r="30" ht="45" customHeight="1">
       <x:c r="A30" s="15" t="str">
         <x:v>02_権限基本設計書</x:v>
       </x:c>
@@ -1515,7 +1557,7 @@
       <x:c r="C30" s="15"/>
       <x:c r="D30" s="15"/>
       <x:c r="E30" s="15" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>&lt;&lt;適用時の正本Version&gt;&gt;</x:v>
       </x:c>
       <x:c r="F30" s="15"/>
       <x:c r="G30" s="15"/>
@@ -1527,7 +1569,7 @@
       <x:c r="K30" s="15"/>
       <x:c r="L30" s="15"/>
     </x:row>
-    <x:row r="31" ht="34" customHeight="1">
+    <x:row r="31" ht="45" customHeight="1">
       <x:c r="A31" s="14" t="str">
         <x:v>16_業務ルールと状態遷移_基本設計書</x:v>
       </x:c>
@@ -1535,7 +1577,7 @@
       <x:c r="C31" s="14"/>
       <x:c r="D31" s="14"/>
       <x:c r="E31" s="14" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>&lt;&lt;適用時の正本Version&gt;&gt;</x:v>
       </x:c>
       <x:c r="F31" s="14"/>
       <x:c r="G31" s="14"/>
@@ -1547,7 +1589,7 @@
       <x:c r="K31" s="14"/>
       <x:c r="L31" s="14"/>
     </x:row>
-    <x:row r="32" ht="34" customHeight="1">
+    <x:row r="32" ht="45" customHeight="1">
       <x:c r="A32" s="15" t="str">
         <x:v>17_トランザクションと排他_基本設計書</x:v>
       </x:c>
@@ -1555,7 +1597,7 @@
       <x:c r="C32" s="15"/>
       <x:c r="D32" s="15"/>
       <x:c r="E32" s="15" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>&lt;&lt;適用時の正本Version&gt;&gt;</x:v>
       </x:c>
       <x:c r="F32" s="15"/>
       <x:c r="G32" s="15"/>
@@ -1567,7 +1609,7 @@
       <x:c r="K32" s="15"/>
       <x:c r="L32" s="15"/>
     </x:row>
-    <x:row r="33" ht="34" customHeight="1">
+    <x:row r="33" ht="45" customHeight="1">
       <x:c r="A33" s="14" t="str">
         <x:v>19_ログファイルRedisセキュリティ_基本設計書</x:v>
       </x:c>
@@ -1575,7 +1617,7 @@
       <x:c r="C33" s="14"/>
       <x:c r="D33" s="14"/>
       <x:c r="E33" s="14" t="str">
-        <x:v>Ver.2.6</x:v>
+        <x:v>&lt;&lt;適用時の正本Version&gt;&gt;</x:v>
       </x:c>
       <x:c r="F33" s="14"/>
       <x:c r="G33" s="14"/>
@@ -1634,7 +1676,6 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A10:L10"/>
     <x:mergeCell ref="A14:L14"/>
@@ -1665,19 +1706,14 @@
     <x:mergeCell ref="E28:H28"/>
     <x:mergeCell ref="I28:L28"/>
     <x:mergeCell ref="A29:D29"/>
-    <x:mergeCell ref="E29:H29"/>
     <x:mergeCell ref="I29:L29"/>
     <x:mergeCell ref="A30:D30"/>
-    <x:mergeCell ref="E30:H30"/>
     <x:mergeCell ref="I30:L30"/>
     <x:mergeCell ref="A31:D31"/>
-    <x:mergeCell ref="E31:H31"/>
     <x:mergeCell ref="I31:L31"/>
     <x:mergeCell ref="A32:D32"/>
-    <x:mergeCell ref="E32:H32"/>
     <x:mergeCell ref="I32:L32"/>
     <x:mergeCell ref="A33:D33"/>
-    <x:mergeCell ref="E33:H33"/>
     <x:mergeCell ref="I33:L33"/>
     <x:mergeCell ref="A34:D34"/>
     <x:mergeCell ref="E34:H34"/>
@@ -1685,6 +1721,12 @@
     <x:mergeCell ref="A35:D35"/>
     <x:mergeCell ref="E35:H35"/>
     <x:mergeCell ref="I35:L35"/>
+    <x:mergeCell ref="A3:L3"/>
+    <x:mergeCell ref="E29:H29"/>
+    <x:mergeCell ref="E30:H30"/>
+    <x:mergeCell ref="E31:H31"/>
+    <x:mergeCell ref="E32:H32"/>
+    <x:mergeCell ref="E33:H33"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -1747,7 +1789,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -2056,10 +2098,10 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A10:L10"/>
     <x:mergeCell ref="A14:L14"/>
+    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2122,7 +2164,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -2563,7 +2605,6 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A5:L5"/>
     <x:mergeCell ref="A7:L7"/>
     <x:mergeCell ref="A8:D8"/>
@@ -2597,6 +2638,7 @@
     <x:mergeCell ref="A31:D31"/>
     <x:mergeCell ref="E31:H31"/>
     <x:mergeCell ref="I31:L31"/>
+    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -2659,7 +2701,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -3096,7 +3138,6 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A7:B7"/>
     <x:mergeCell ref="C7:D7"/>
@@ -3159,6 +3200,7 @@
     <x:mergeCell ref="D31:F31"/>
     <x:mergeCell ref="G31:I31"/>
     <x:mergeCell ref="J31:L31"/>
+    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -3221,7 +3263,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：Review中</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：Review済／承認待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -3482,7 +3524,6 @@
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="I1:L1"/>
     <x:mergeCell ref="I2:L2"/>
-    <x:mergeCell ref="A3:L3"/>
     <x:mergeCell ref="A6:L6"/>
     <x:mergeCell ref="A7:L7"/>
     <x:mergeCell ref="A8:L8"/>
@@ -3496,6 +3537,7 @@
     <x:mergeCell ref="A19:D19"/>
     <x:mergeCell ref="E19:H19"/>
     <x:mergeCell ref="I19:L19"/>
+    <x:mergeCell ref="A3:L3"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/詳細設計/01E_DB詳細設計書テンプレート.xlsx
+++ b/詳細設計/01E_DB詳細設計書テンプレート.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="R069c5d289c91480b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="Rec3e6f26c957423e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Table一覧・作成順" sheetId="3" r:id="R2f5c92256fa34e37"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_ER・制約一覧" sheetId="4" r:id="R2d7ce43fb2c147b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Table詳細・DDL" sheetId="5" r:id="Reebfb474208e4923"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_Status・初期Data" sheetId="6" r:id="Rb77b537a16fe42e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_単体テスト観点" sheetId="7" r:id="R0507dc970c5140b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_表紙" sheetId="1" r:id="Re4802f94ebb24129"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_改訂履歴" sheetId="2" r:id="R33beb13113bc4078"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Table一覧・作成順" sheetId="3" r:id="Rfd0fd80af7a14e89"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_ER・制約一覧" sheetId="4" r:id="R648afa381ef64843"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Table詳細・DDL" sheetId="5" r:id="Rbb21900d9f1d4eec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="99_Status・初期Data" sheetId="6" r:id="R1823e6a7489d4c91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_単体テスト観点" sheetId="7" r:id="Rf34e13111846477f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -602,7 +602,7 @@
       <x:c r="G2" s="3"/>
       <x:c r="H2" s="3"/>
       <x:c r="I2" s="1" t="str">
-        <x:v>Ver.2.4　2026-10-09</x:v>
+        <x:v>Ver.2.5　2026-10-15</x:v>
       </x:c>
       <x:c r="J2" s="1"/>
       <x:c r="K2" s="1"/>
@@ -610,7 +610,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="1" t="str">
-        <x:v>Company WorkHub　詳細設計　／　状態：修正済／承認待ち</x:v>
+        <x:v>Company WorkHub　詳細設計　／　状態：修正済／Review待ち</x:v>
       </x:c>
       <x:c r="B3" s="1"/>
       <x:c r="C3" s="1"/>
@@ -700,7 +700,7 @@
       <x:c r="E9" s="15"/>
       <x:c r="F9" s="15"/>
       <x:c r="G9" s="15" t="str">
-        <x:v>Ver.2.4</x:v>
+        <x:v>Ver.2.5</x:v>
       </x:c>
       <x:c r="H9" s="15"/>
       <x:c r="I9" s="15"/>
@@ -718,7 +718,7 @@
       <x:c r="E10" s="14"/>
       <x:c r="F10" s="14"/>
       <x:c r="G10" s="14" t="str">
-        <x:v>2026-10-09</x:v>
+        <x:v>2026-10-15</x:v>
       </x:c>
       <x:c r="H10" s="14"/>
       <x:c r="I10" s="14"/>
@@ -754,7 +754,7 @@
       <x:c r="E12" s="14"/>
       <x:c r="F12" s="14"/>
       <x:c r="G12" s="14" t="str">
-        <x:v>修正済／承認待ち</x:v>
+        <x:v>修正済／Review待ち</x:v>
       </x:c>
       <x:c r="H12" s="14"/>
       <x:c r="I12" s="14"/>
@@ -969,7 +969,7 @@
       <x:c r="G2" s="3"/>
       <x:c r="H2" s="3"/>
       <x:c r="I2" s="1" t="str">
-        <x:v>Ver.2.4　2026-10-09</x:v>
+        <x:v>Ver.2.5　2026-10-15</x:v>
       </x:c>
       <x:c r="J2" s="1"/>
       <x:c r="K2" s="1"/>
@@ -1212,6 +1212,35 @@
         <x:v>承認待ち</x:v>
       </x:c>
       <x:c r="L13" s="28"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="28" t="str">
+        <x:v>Ver.2.5</x:v>
+      </x:c>
+      <x:c r="B14" s="28" t="str">
+        <x:v>2026-10-15</x:v>
+      </x:c>
+      <x:c r="C14" s="28"/>
+      <x:c r="D14" s="28" t="str">
+        <x:v>改訂</x:v>
+      </x:c>
+      <x:c r="E14" s="28" t="str">
+        <x:v>DB試験観点の期待条件と上流根拠の記載方式を明確化。</x:v>
+      </x:c>
+      <x:c r="F14" s="28"/>
+      <x:c r="G14" s="28" t="str">
+        <x:v>Project Leader</x:v>
+      </x:c>
+      <x:c r="H14" s="28" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="I14" s="28"/>
+      <x:c r="J14" s="28" t="str">
+        <x:v>－</x:v>
+      </x:c>
+      <x:c r="K14" s="28" t="str">
+        <x:v>Review待ち</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
@@ -1302,7 +1331,7 @@
       <x:c r="G2" s="3"/>
       <x:c r="H2" s="3"/>
       <x:c r="I2" s="1" t="str">
-        <x:v>Ver.2.4　2026-10-09</x:v>
+        <x:v>Ver.2.5　2026-10-15</x:v>
       </x:c>
       <x:c r="J2" s="1"/>
       <x:c r="K2" s="1"/>
@@ -2004,7 +2033,7 @@
       <x:c r="G2" s="3"/>
       <x:c r="H2" s="3"/>
       <x:c r="I2" s="1" t="str">
-        <x:v>Ver.2.4　2026-10-09</x:v>
+        <x:v>Ver.2.5　2026-10-15</x:v>
       </x:c>
       <x:c r="J2" s="1"/>
       <x:c r="K2" s="1"/>
@@ -2409,7 +2438,7 @@
       <x:c r="G2" s="3"/>
       <x:c r="H2" s="3"/>
       <x:c r="I2" s="1" t="str">
-        <x:v>Ver.2.4　2026-10-09</x:v>
+        <x:v>Ver.2.5　2026-10-15</x:v>
       </x:c>
       <x:c r="J2" s="1"/>
       <x:c r="K2" s="1"/>
@@ -3025,7 +3054,7 @@
       <x:c r="G2" s="3"/>
       <x:c r="H2" s="3"/>
       <x:c r="I2" s="1" t="str">
-        <x:v>Ver.2.4　2026-10-09</x:v>
+        <x:v>Ver.2.5　2026-10-15</x:v>
       </x:c>
       <x:c r="J2" s="1"/>
       <x:c r="K2" s="1"/>
@@ -3533,7 +3562,7 @@
       <x:c r="G2" s="3"/>
       <x:c r="H2" s="3"/>
       <x:c r="I2" s="1" t="str">
-        <x:v>Ver.2.4　2026-10-09</x:v>
+        <x:v>Ver.2.5　2026-10-15</x:v>
       </x:c>
       <x:c r="J2" s="1"/>
       <x:c r="K2" s="1"/>
@@ -3571,7 +3600,7 @@
     </x:row>
     <x:row r="5" ht="34" customHeight="1">
       <x:c r="A5" s="50" t="str">
-        <x:v>本SheetはDB設計から単体テスト仕様書へ引き渡す観点だけを記載する。具体Case、SQL、実施結果、証跡は別冊の単体テスト仕様書またはCIで管理する。</x:v>
+        <x:v>本SheetはDB構造から導くテスト観点と期待条件を記載する。具体的なFixture・実行SQL・証跡・結果は単体テスト仕様書／CIで管理する。対象制約と成功件数／SQLSTATE、基本設計File／Sheet／設計ID又はCell位置を明記する。</x:v>
       </x:c>
       <x:c r="B5" s="50"/>
       <x:c r="C5" s="50"/>
@@ -3624,7 +3653,7 @@
         <x:v>期待条件</x:v>
       </x:c>
       <x:c r="D8" s="39" t="str">
-        <x:v>参照</x:v>
+        <x:v>基本／詳細設計参照</x:v>
       </x:c>
       <x:c r="E8"/>
       <x:c r="F8"/>
@@ -3646,7 +3675,7 @@
         <x:v>&lt;&lt;成功条件/SQLSTATE/件数&gt;&gt;</x:v>
       </x:c>
       <x:c r="D9" s="42" t="str">
-        <x:v>&lt;&lt;03/04/基本設計ID&gt;&gt;</x:v>
+        <x:v>&lt;&lt;15_DB基本設計書／Sheet／Table.Column又はCell、03／04設計ID&gt;&gt;</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="29" customHeight="1">
